--- a/base/StructureDefinition-SGQuestionnaire.xlsx
+++ b/base/StructureDefinition-SGQuestionnaire.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}que-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}que-2:The link ids for groups and questions must be unique within the questionnaire {descendants().linkId.isDistinct()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}que-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}que-2:The link ids for groups and questions must be unique within the questionnaire {descendants().linkId.isDistinct()}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>Observation[moodCode=DEF]</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -426,6 +426,9 @@
     <t>Questionnaire.extension</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -466,20 +469,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>Questionnaire.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
+    <t>ele-1
+shr-1</t>
   </si>
   <si>
     <t>Questionnaire.extension:versionAlgorithm</t>
@@ -501,6 +492,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Questionnaire.extension:versionPolicy</t>
   </si>
   <si>
@@ -517,6 +512,48 @@
     <t>Defines the versioning policy of the artifact.</t>
   </si>
   <si>
+    <t>Questionnaire.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://smart.who.int/base/StructureDefinition/SGActorExt}
+</t>
+  </si>
+  <si>
+    <t>Smart Guidelines Actor Reference extension</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:task</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://smart.who.int/base/StructureDefinition/SGcode}
+</t>
+  </si>
+  <si>
+    <t>Smart Guidelines code extension</t>
+  </si>
+  <si>
     <t>Questionnaire.modifierExtension</t>
   </si>
   <si>
@@ -657,7 +694,7 @@
     <t>Questionnaire.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Questionnaire)
+    <t xml:space="preserve">canonical(Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -893,7 +930,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -1026,7 +1063,7 @@
     <t>Codes for questionnaires, groups and individual questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -1278,7 +1315,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringCodingQuantityReference(Resource)</t>
+decimalintegerdatedateTimetimestringCodingQuantityReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Value for question comparison based on operator</t>
@@ -1290,7 +1327,7 @@
     <t>Allowed values to answer questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">que-7
@@ -1397,7 +1434,7 @@
     <t>Questionnaire.item.answerValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -1439,7 +1476,7 @@
   </si>
   <si>
     <t>integer
-datetimestringCodingReference(Resource)</t>
+datetimestringCodingReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Answer value</t>
@@ -1498,7 +1535,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource)</t>
+decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Actual value for initializing the question</t>
@@ -1846,20 +1883,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.5078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.5078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.15234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.15234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.84765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1868,27 +1905,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.10546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.78515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.04296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="121.0546875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="25.01171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="107.96875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2844,7 +2881,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>84</v>
@@ -2859,13 +2896,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2904,17 +2941,17 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>83</v>
@@ -2926,7 +2963,7 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2944,15 +2981,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
@@ -2974,13 +3011,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3031,7 +3068,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>83</v>
@@ -3040,10 +3077,10 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3061,15 +3098,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3079,7 +3116,7 @@
         <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>88</v>
@@ -3091,15 +3128,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3148,7 +3187,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -3157,10 +3196,10 @@
         <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3180,13 +3219,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3199,7 +3238,7 @@
         <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3208,17 +3247,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3267,7 +3304,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3276,10 +3313,10 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3297,15 +3334,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3327,13 +3364,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3384,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -3393,10 +3430,10 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3416,18 +3453,20 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>84</v>
@@ -3436,26 +3475,22 @@
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3503,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3515,10 +3550,10 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3538,9 +3573,11 @@
         <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3549,32 +3586,28 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3622,28 +3655,28 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3654,14 +3687,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3674,25 +3707,25 @@
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3741,7 +3774,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3753,30 +3786,30 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3799,18 +3832,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3858,7 +3893,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -3873,13 +3908,13 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -3890,10 +3925,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3901,13 +3936,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3916,19 +3951,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3977,42 +4012,42 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4035,16 +4070,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4094,7 +4129,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4109,27 +4144,27 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4137,32 +4172,34 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4211,42 +4248,42 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4263,22 +4300,22 @@
         <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4304,13 +4341,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4328,10 +4365,10 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -4343,13 +4380,13 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4360,10 +4397,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4371,34 +4408,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4447,13 +4482,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4462,13 +4497,13 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4477,12 +4512,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4490,16 +4525,16 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
@@ -4508,13 +4543,13 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4540,13 +4575,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4564,13 +4599,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4579,13 +4614,13 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4594,26 +4629,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4622,18 +4657,20 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4681,7 +4718,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -4696,13 +4733,13 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>130</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4713,10 +4750,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4724,13 +4761,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4739,20 +4776,18 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4776,13 +4811,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4800,13 +4835,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4815,13 +4850,13 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4832,21 +4867,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4858,16 +4893,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4917,13 +4952,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4932,13 +4967,13 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4947,12 +4982,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4972,21 +5007,23 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5034,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5049,13 +5086,13 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -5066,10 +5103,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5092,20 +5129,18 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5153,7 +5188,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5168,10 +5203,10 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5183,12 +5218,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5196,31 +5231,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5246,13 +5281,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5270,13 +5305,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5285,10 +5320,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>189</v>
+        <v>276</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5302,10 +5337,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5316,7 +5351,7 @@
         <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5325,21 +5360,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5387,13 +5424,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5402,16 +5439,16 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5419,21 +5456,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5442,21 +5479,21 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5480,13 +5517,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5504,13 +5541,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5519,16 +5556,16 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5536,10 +5573,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5562,16 +5599,16 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5621,7 +5658,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -5636,16 +5673,16 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5653,14 +5690,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5679,19 +5716,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5740,7 +5775,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -5755,16 +5790,16 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5772,10 +5807,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5795,23 +5830,21 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5859,7 +5892,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -5874,16 +5907,16 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5891,10 +5924,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5905,7 +5938,7 @@
         <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5914,20 +5947,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5952,13 +5987,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5976,13 +6011,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5991,16 +6026,16 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6008,10 +6043,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6022,7 +6057,7 @@
         <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6031,21 +6066,23 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6093,31 +6130,31 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>332</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>200</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6125,10 +6162,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6139,7 +6176,7 @@
         <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6148,19 +6185,21 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6184,13 +6223,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6208,22 +6247,22 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6240,14 +6279,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6266,16 +6305,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6325,7 +6364,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6334,13 +6373,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6357,46 +6396,42 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6444,22 +6479,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>130</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6476,21 +6511,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6502,20 +6537,18 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6563,22 +6596,22 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6602,38 +6635,38 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>358</v>
+        <v>176</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6682,22 +6715,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>359</v>
+        <v>130</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6714,10 +6747,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6725,10 +6758,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6740,19 +6773,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>318</v>
+        <v>196</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6777,13 +6810,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6801,22 +6834,22 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6840,7 +6873,7 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6859,19 +6892,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6935,7 +6968,7 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
@@ -6952,10 +6985,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6966,7 +6999,7 @@
         <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6978,18 +7011,20 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>185</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7013,13 +7048,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7037,22 +7072,22 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -7076,11 +7111,11 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>79</v>
@@ -7095,19 +7130,19 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7132,13 +7167,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7159,7 +7194,7 @@
         <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>79</v>
@@ -7171,7 +7206,7 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -7188,10 +7223,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7202,32 +7237,30 @@
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>327</v>
+        <v>196</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7275,22 +7308,22 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>389</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
@@ -7307,10 +7340,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7318,7 +7351,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>79</v>
@@ -7333,16 +7366,20 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7366,13 +7403,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7390,10 +7427,10 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>79</v>
@@ -7402,10 +7439,10 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
@@ -7422,14 +7459,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7442,24 +7479,26 @@
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>340</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7507,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -7519,10 +7558,10 @@
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>400</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -7539,46 +7578,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7626,22 +7661,22 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>130</v>
+        <v>349</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7658,21 +7693,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7684,16 +7719,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>175</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7743,22 +7778,22 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7775,42 +7810,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7834,13 +7873,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7858,22 +7897,22 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>130</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
@@ -7890,10 +7929,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7916,15 +7955,17 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>403</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7949,13 +7990,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>407</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7973,7 +8014,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7982,13 +8023,13 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>20</v>
@@ -8005,10 +8046,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8016,7 +8057,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>79</v>
@@ -8034,14 +8075,12 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>412</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8066,13 +8105,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="Y53" t="s" s="2">
         <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8090,22 +8129,22 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
@@ -8122,10 +8161,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8133,7 +8172,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>79</v>
@@ -8148,83 +8187,79 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q54" t="s" s="2">
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
@@ -8241,10 +8276,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8267,85 +8302,81 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="O55" t="s" s="2">
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="R55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8362,10 +8393,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8388,83 +8419,83 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="O56" t="s" s="2">
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8481,10 +8512,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8507,22 +8538,26 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8566,7 +8601,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -8575,13 +8610,13 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>20</v>
@@ -8593,15 +8628,15 @@
         <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8624,18 +8659,20 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8683,7 +8720,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -8692,13 +8729,13 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
@@ -8715,10 +8752,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8729,7 +8766,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8741,7 +8778,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>327</v>
+        <v>445</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>446</v>
@@ -8800,22 +8837,22 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
@@ -8827,15 +8864,15 @@
         <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8858,15 +8895,17 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>185</v>
+        <v>451</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>335</v>
+        <v>452</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8915,7 +8954,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>337</v>
+        <v>450</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -8924,13 +8963,13 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>20</v>
@@ -8947,14 +8986,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8973,16 +9012,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>340</v>
+        <v>457</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>164</v>
+        <v>459</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9032,7 +9071,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9041,13 +9080,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>20</v>
@@ -9064,46 +9103,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9151,22 +9186,22 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>130</v>
+        <v>349</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -9183,21 +9218,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9209,16 +9244,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>453</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>351</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>352</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>456</v>
+        <v>175</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9244,13 +9279,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>407</v>
+        <v>20</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9268,22 +9303,22 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>452</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9300,50 +9335,50 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>458</v>
+        <v>356</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>459</v>
+        <v>357</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9387,22 +9422,22 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>457</v>
+        <v>358</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>383</v>
+        <v>130</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>20</v>
@@ -9419,10 +9454,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9430,10 +9465,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9445,20 +9480,18 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>327</v>
+        <v>464</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -9482,13 +9515,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>20</v>
+        <v>418</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9506,22 +9539,22 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>467</v>
+        <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
@@ -9564,20 +9597,24 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="R66" t="s" s="2">
         <v>20</v>
       </c>
@@ -9621,7 +9658,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>337</v>
+        <v>468</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -9633,10 +9670,10 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
@@ -9653,14 +9690,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9679,18 +9716,20 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>340</v>
+        <v>474</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>341</v>
+        <v>475</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
       </c>
@@ -9738,7 +9777,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>342</v>
+        <v>473</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -9747,13 +9786,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>20</v>
+        <v>478</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
@@ -9770,46 +9809,42 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -9857,22 +9892,22 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>130</v>
+        <v>349</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -9889,21 +9924,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9915,16 +9950,16 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>472</v>
+        <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>473</v>
+        <v>351</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>474</v>
+        <v>352</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9950,13 +9985,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>407</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9974,22 +10009,22 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>471</v>
+        <v>353</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -10006,14 +10041,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10026,25 +10061,25 @@
         <v>20</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>477</v>
+        <v>356</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>478</v>
+        <v>357</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>479</v>
+        <v>175</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>480</v>
+        <v>176</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10093,7 +10128,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>476</v>
+        <v>358</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -10102,39 +10137,275 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>481</v>
+        <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AK71" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AO72">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
